--- a/data/sample/input1_objetivo.xlsx
+++ b/data/sample/input1_objetivo.xlsx
@@ -475,13 +475,13 @@
         <v>90020001</v>
       </c>
       <c r="D4" t="n">
-        <v>143629714.1</v>
+        <v>138763519.92</v>
       </c>
       <c r="E4" t="n">
-        <v>8120.07</v>
+        <v>7961.42</v>
       </c>
       <c r="F4" t="n">
-        <v>148656754.09</v>
+        <v>143620243.12</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -504,13 +504,13 @@
         <v>90020002</v>
       </c>
       <c r="D5" t="n">
-        <v>246872989.12</v>
+        <v>248354149.57</v>
       </c>
       <c r="E5" t="n">
-        <v>16198.8</v>
+        <v>17958.88</v>
       </c>
       <c r="F5" t="n">
-        <v>255513543.74</v>
+        <v>257046544.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -533,13 +533,13 @@
         <v>90020003</v>
       </c>
       <c r="D6" t="n">
-        <v>230372407.56</v>
+        <v>178485246.07</v>
       </c>
       <c r="E6" t="n">
-        <v>16019.76</v>
+        <v>12926.15</v>
       </c>
       <c r="F6" t="n">
-        <v>238435441.82</v>
+        <v>184732229.68</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -591,13 +591,13 @@
         <v>90020005</v>
       </c>
       <c r="D8" t="n">
-        <v>268727471.16</v>
+        <v>219143256.06</v>
       </c>
       <c r="E8" t="n">
-        <v>16044.4</v>
+        <v>13378.5</v>
       </c>
       <c r="F8" t="n">
-        <v>278132932.65</v>
+        <v>226813270.02</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -620,13 +620,13 @@
         <v>90020006</v>
       </c>
       <c r="D9" t="n">
-        <v>114775530.82</v>
+        <v>95317256.75</v>
       </c>
       <c r="E9" t="n">
-        <v>9264.940000000001</v>
+        <v>7165.62</v>
       </c>
       <c r="F9" t="n">
-        <v>118792674.4</v>
+        <v>98653360.73999999</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -649,13 +649,13 @@
         <v>90020007</v>
       </c>
       <c r="D10" t="n">
-        <v>192030566.35</v>
+        <v>224989345.49</v>
       </c>
       <c r="E10" t="n">
-        <v>13960.46</v>
+        <v>16234.03</v>
       </c>
       <c r="F10" t="n">
-        <v>198751636.17</v>
+        <v>232863972.58</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -678,13 +678,13 @@
         <v>90020008</v>
       </c>
       <c r="D11" t="n">
-        <v>168648232.19</v>
+        <v>201944633.32</v>
       </c>
       <c r="E11" t="n">
-        <v>12584.24</v>
+        <v>13993.95</v>
       </c>
       <c r="F11" t="n">
-        <v>174550920.32</v>
+        <v>209012695.49</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -707,13 +707,13 @@
         <v>90020009</v>
       </c>
       <c r="D12" t="n">
-        <v>26350271.5</v>
+        <v>25455900</v>
       </c>
       <c r="E12" t="n">
-        <v>1576.4</v>
+        <v>1479.6</v>
       </c>
       <c r="F12" t="n">
-        <v>27272531</v>
+        <v>26346856.5</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         <v>90020010</v>
       </c>
       <c r="D13" t="n">
-        <v>155626842.14</v>
+        <v>114082726.02</v>
       </c>
       <c r="E13" t="n">
-        <v>10298.74</v>
+        <v>7664.68</v>
       </c>
       <c r="F13" t="n">
-        <v>161073781.61</v>
+        <v>118075621.43</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -765,13 +765,13 @@
         <v>90020011</v>
       </c>
       <c r="D14" t="n">
-        <v>226094262.95</v>
+        <v>203579936.42</v>
       </c>
       <c r="E14" t="n">
-        <v>14744.31</v>
+        <v>12581.34</v>
       </c>
       <c r="F14" t="n">
-        <v>234007562.15</v>
+        <v>210705234.19</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -794,13 +794,13 @@
         <v>90020012</v>
       </c>
       <c r="D15" t="n">
-        <v>219790304.7</v>
+        <v>271956687.18</v>
       </c>
       <c r="E15" t="n">
-        <v>12622.12</v>
+        <v>15346.27</v>
       </c>
       <c r="F15" t="n">
-        <v>227482965.36</v>
+        <v>281475171.23</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -823,13 +823,13 @@
         <v>90020013</v>
       </c>
       <c r="D16" t="n">
-        <v>197758313.01</v>
+        <v>229321815.23</v>
       </c>
       <c r="E16" t="n">
-        <v>11800.97</v>
+        <v>14243.11</v>
       </c>
       <c r="F16" t="n">
-        <v>204679853.97</v>
+        <v>237348078.76</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -852,13 +852,13 @@
         <v>90020014</v>
       </c>
       <c r="D17" t="n">
-        <v>63533897.44</v>
+        <v>81845440.3</v>
       </c>
       <c r="E17" t="n">
-        <v>4466.7</v>
+        <v>5529.88</v>
       </c>
       <c r="F17" t="n">
-        <v>65757583.85</v>
+        <v>84710030.70999999</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,13 +881,13 @@
         <v>90020015</v>
       </c>
       <c r="D18" t="n">
-        <v>37189741</v>
+        <v>48585891.2</v>
       </c>
       <c r="E18" t="n">
-        <v>2473.1</v>
+        <v>3271.6</v>
       </c>
       <c r="F18" t="n">
-        <v>38491381.94</v>
+        <v>50286397.39</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -910,13 +910,13 @@
         <v>90020016</v>
       </c>
       <c r="D19" t="n">
-        <v>301398937.45</v>
+        <v>231833548.12</v>
       </c>
       <c r="E19" t="n">
-        <v>18744.49</v>
+        <v>16109.86</v>
       </c>
       <c r="F19" t="n">
-        <v>311947900.26</v>
+        <v>239947722.3</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -939,13 +939,13 @@
         <v>90020017</v>
       </c>
       <c r="D20" t="n">
-        <v>142176434.64</v>
+        <v>149452277.6</v>
       </c>
       <c r="E20" t="n">
-        <v>7924.68</v>
+        <v>8057.6</v>
       </c>
       <c r="F20" t="n">
-        <v>147152609.85</v>
+        <v>154683107.32</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -968,13 +968,13 @@
         <v>90020018</v>
       </c>
       <c r="D21" t="n">
-        <v>173565751.04</v>
+        <v>148105560.5</v>
       </c>
       <c r="E21" t="n">
-        <v>12864.94</v>
+        <v>10916.99</v>
       </c>
       <c r="F21" t="n">
-        <v>179640552.33</v>
+        <v>153289255.12</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -997,13 +997,13 @@
         <v>90020019</v>
       </c>
       <c r="D22" t="n">
-        <v>110189626.12</v>
+        <v>134907619.86</v>
       </c>
       <c r="E22" t="n">
-        <v>5433.96</v>
+        <v>6661.18</v>
       </c>
       <c r="F22" t="n">
-        <v>114046263.03</v>
+        <v>139629386.56</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1026,13 +1026,13 @@
         <v>90020020</v>
       </c>
       <c r="D23" t="n">
-        <v>246729153.16</v>
+        <v>236754000.88</v>
       </c>
       <c r="E23" t="n">
-        <v>14522.8</v>
+        <v>14039.36</v>
       </c>
       <c r="F23" t="n">
-        <v>255364673.52</v>
+        <v>245040390.91</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1055,13 +1055,13 @@
         <v>90020101</v>
       </c>
       <c r="D24" t="n">
-        <v>248854473.99</v>
+        <v>137965805.83</v>
       </c>
       <c r="E24" t="n">
-        <v>13811.42</v>
+        <v>7653.37</v>
       </c>
       <c r="F24" t="n">
-        <v>257564380.58</v>
+        <v>142794609.03</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1084,13 +1084,13 @@
         <v>90020102</v>
       </c>
       <c r="D25" t="n">
-        <v>267753858.05</v>
+        <v>205352868.5</v>
       </c>
       <c r="E25" t="n">
-        <v>13942.99</v>
+        <v>12508.05</v>
       </c>
       <c r="F25" t="n">
-        <v>277125243.08</v>
+        <v>212540218.9</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1113,13 +1113,13 @@
         <v>90020103</v>
       </c>
       <c r="D26" t="n">
-        <v>186327346.47</v>
+        <v>173045180.69</v>
       </c>
       <c r="E26" t="n">
-        <v>12133.14</v>
+        <v>12271.01</v>
       </c>
       <c r="F26" t="n">
-        <v>192848803.6</v>
+        <v>179101762.01</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1142,13 +1142,13 @@
         <v>90020104</v>
       </c>
       <c r="D27" t="n">
-        <v>327014978.69</v>
+        <v>106401780.9</v>
       </c>
       <c r="E27" t="n">
-        <v>14659.12</v>
+        <v>8808.76</v>
       </c>
       <c r="F27" t="n">
-        <v>338460502.94</v>
+        <v>110125843.23</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         <v>90020105</v>
       </c>
       <c r="D28" t="n">
-        <v>193004841.08</v>
+        <v>278553398.45</v>
       </c>
       <c r="E28" t="n">
-        <v>11598.16</v>
+        <v>16786.21</v>
       </c>
       <c r="F28" t="n">
-        <v>199760010.52</v>
+        <v>288302767.4</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1229,13 +1229,13 @@
         <v>90020107</v>
       </c>
       <c r="D30" t="n">
-        <v>86263996.44</v>
+        <v>92077430.28</v>
       </c>
       <c r="E30" t="n">
-        <v>5178.91</v>
+        <v>5301.56</v>
       </c>
       <c r="F30" t="n">
-        <v>89283236.31999999</v>
+        <v>95300140.34</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1258,13 +1258,13 @@
         <v>90020108</v>
       </c>
       <c r="D31" t="n">
-        <v>135946846.08</v>
+        <v>126186915.35</v>
       </c>
       <c r="E31" t="n">
-        <v>6834.68</v>
+        <v>5200.08</v>
       </c>
       <c r="F31" t="n">
-        <v>140704985.69</v>
+        <v>130603457.39</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1287,13 +1287,13 @@
         <v>90020109</v>
       </c>
       <c r="D32" t="n">
-        <v>289936797.49</v>
+        <v>154913492.32</v>
       </c>
       <c r="E32" t="n">
-        <v>18499.03</v>
+        <v>8132.36</v>
       </c>
       <c r="F32" t="n">
-        <v>300084585.4</v>
+        <v>160335464.55</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1316,13 +1316,13 @@
         <v>90020110</v>
       </c>
       <c r="D33" t="n">
-        <v>343930242.91</v>
+        <v>235364842.38</v>
       </c>
       <c r="E33" t="n">
-        <v>20475.07</v>
+        <v>15350.09</v>
       </c>
       <c r="F33" t="n">
-        <v>355967801.41</v>
+        <v>243602611.86</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1345,13 +1345,13 @@
         <v>90020111</v>
       </c>
       <c r="D34" t="n">
-        <v>180158805.8</v>
+        <v>368974015.12</v>
       </c>
       <c r="E34" t="n">
-        <v>7462.73</v>
+        <v>21871.53</v>
       </c>
       <c r="F34" t="n">
-        <v>186464364</v>
+        <v>381888105.65</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1374,13 +1374,13 @@
         <v>90020112</v>
       </c>
       <c r="D35" t="n">
-        <v>131271026.58</v>
+        <v>147137878.12</v>
       </c>
       <c r="E35" t="n">
-        <v>6850.9</v>
+        <v>8167.87</v>
       </c>
       <c r="F35" t="n">
-        <v>135865512.51</v>
+        <v>152287703.85</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1403,13 +1403,13 @@
         <v>90020113</v>
       </c>
       <c r="D36" t="n">
-        <v>284484265.96</v>
+        <v>140369928.96</v>
       </c>
       <c r="E36" t="n">
-        <v>12597.56</v>
+        <v>8516</v>
       </c>
       <c r="F36" t="n">
-        <v>294441215.27</v>
+        <v>145282876.47</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1432,13 +1432,13 @@
         <v>90020114</v>
       </c>
       <c r="D37" t="n">
-        <v>273494927.83</v>
+        <v>44452767.96</v>
       </c>
       <c r="E37" t="n">
-        <v>15468.63</v>
+        <v>2603.2</v>
       </c>
       <c r="F37" t="n">
-        <v>283067250.3</v>
+        <v>46008614.84</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1461,13 +1461,13 @@
         <v>90020115</v>
       </c>
       <c r="D38" t="n">
-        <v>152623864.8</v>
+        <v>264740056.08</v>
       </c>
       <c r="E38" t="n">
-        <v>8250.370000000001</v>
+        <v>16545.66</v>
       </c>
       <c r="F38" t="n">
-        <v>157965700.07</v>
+        <v>274005958.04</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1490,13 +1490,13 @@
         <v>90020116</v>
       </c>
       <c r="D39" t="n">
-        <v>87353478.62</v>
+        <v>98017658.52</v>
       </c>
       <c r="E39" t="n">
-        <v>8329.459999999999</v>
+        <v>6402.66</v>
       </c>
       <c r="F39" t="n">
-        <v>90410850.37</v>
+        <v>101448276.57</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1519,13 +1519,13 @@
         <v>90020117</v>
       </c>
       <c r="D40" t="n">
-        <v>294604615.46</v>
+        <v>105550382.26</v>
       </c>
       <c r="E40" t="n">
-        <v>13994.48</v>
+        <v>9206.799999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>304915777</v>
+        <v>109244645.64</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1548,13 +1548,13 @@
         <v>90020118</v>
       </c>
       <c r="D41" t="n">
-        <v>158566865.91</v>
+        <v>267850455.88</v>
       </c>
       <c r="E41" t="n">
-        <v>11180.13</v>
+        <v>13244.58</v>
       </c>
       <c r="F41" t="n">
-        <v>164116706.22</v>
+        <v>277225221.84</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1577,13 +1577,13 @@
         <v>90020119</v>
       </c>
       <c r="D42" t="n">
-        <v>231860363.13</v>
+        <v>202683990.08</v>
       </c>
       <c r="E42" t="n">
-        <v>13070.37</v>
+        <v>10971.66</v>
       </c>
       <c r="F42" t="n">
-        <v>239975475.84</v>
+        <v>209777929.73</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1606,13 +1606,13 @@
         <v>90020120</v>
       </c>
       <c r="D43" t="n">
-        <v>223166594.02</v>
+        <v>159286239.09</v>
       </c>
       <c r="E43" t="n">
-        <v>15141.16</v>
+        <v>11861.91</v>
       </c>
       <c r="F43" t="n">
-        <v>230977424.81</v>
+        <v>164861257.46</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1664,13 +1664,13 @@
         <v>90020122</v>
       </c>
       <c r="D45" t="n">
-        <v>234598564.4</v>
+        <v>279107641.96</v>
       </c>
       <c r="E45" t="n">
-        <v>10635.39</v>
+        <v>17164.48</v>
       </c>
       <c r="F45" t="n">
-        <v>242809514.15</v>
+        <v>288876409.43</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1693,13 +1693,13 @@
         <v>90020123</v>
       </c>
       <c r="D46" t="n">
-        <v>387893998.2</v>
+        <v>238622313.68</v>
       </c>
       <c r="E46" t="n">
-        <v>18007.15</v>
+        <v>12352.9</v>
       </c>
       <c r="F46" t="n">
-        <v>401470288.14</v>
+        <v>246974094.66</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1722,13 +1722,13 @@
         <v>90020124</v>
       </c>
       <c r="D47" t="n">
-        <v>117181012.5</v>
+        <v>117350267.58</v>
       </c>
       <c r="E47" t="n">
-        <v>5503.75</v>
+        <v>7682.87</v>
       </c>
       <c r="F47" t="n">
-        <v>121282347.94</v>
+        <v>121457526.95</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1751,13 +1751,13 @@
         <v>90020125</v>
       </c>
       <c r="D48" t="n">
-        <v>204936663.09</v>
+        <v>176950306.16</v>
       </c>
       <c r="E48" t="n">
-        <v>10881.66</v>
+        <v>10847.96</v>
       </c>
       <c r="F48" t="n">
-        <v>212109446.3</v>
+        <v>183143566.88</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>

--- a/data/sample/input1_objetivo.xlsx
+++ b/data/sample/input1_objetivo.xlsx
@@ -463,7 +463,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ingredientes</t>
+          <t>Culinarios</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -492,7 +492,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ingredientes</t>
+          <t>Culinarios</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ingredientes</t>
+          <t>Culinarios</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ingredientes</t>
+          <t>Culinarios</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ingredientes</t>
+          <t>Culinarios</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ingredientes</t>
+          <t>Lácteos</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ingredientes</t>
+          <t>Café</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -666,7 +666,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ingredientes</t>
+          <t>Café</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -695,7 +695,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ingredientes</t>
+          <t>Chocolatería</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ingredientes</t>
+          <t>Lácteos</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ingredientes</t>
+          <t>Culinarios</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -782,7 +782,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ingredientes</t>
+          <t>Lácteos</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ingredientes</t>
+          <t>Chocolatería</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -840,7 +840,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ingredientes</t>
+          <t>Lácteos</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -869,7 +869,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ingredientes</t>
+          <t>Chocolatería</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -898,7 +898,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ingredientes</t>
+          <t>Culinarios</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ingredientes</t>
+          <t>Chocolatería</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -956,7 +956,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ingredientes</t>
+          <t>Chocolatería</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -985,7 +985,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ingredientes</t>
+          <t>Chocolatería</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ingredientes</t>
+          <t>Café</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1043,7 +1043,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Endulzantes</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1072,7 +1072,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Descartables</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,7 +1101,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Café</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1130,7 +1130,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Descartables</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1159,7 +1159,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Endulzantes</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1188,7 +1188,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Café</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1217,7 +1217,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Descartables</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1246,7 +1246,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Descartables</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1275,7 +1275,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Café</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1304,7 +1304,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Endulzantes</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1333,7 +1333,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Descartables</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1362,7 +1362,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Descartables</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1391,7 +1391,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Vajilla</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1420,7 +1420,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Descartables</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Endulzantes</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1478,7 +1478,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Vajilla</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1507,7 +1507,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Endulzantes</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1536,7 +1536,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Endulzantes</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1565,7 +1565,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Vajilla</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1594,7 +1594,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Endulzantes</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1623,7 +1623,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Vajilla</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1652,7 +1652,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Vajilla</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Descartables</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1710,7 +1710,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Descartables</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1739,7 +1739,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Descartables</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1768,7 +1768,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Soluciones</t>
+          <t>Café</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1797,7 +1797,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ingredientes</t>
+          <t>Lácteos</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1826,7 +1826,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ingredientes</t>
+          <t>Café</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
